--- a/блок1.xlsx
+++ b/блок1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Точное решение</t>
   </si>
@@ -29,6 +29,24 @@
   <si>
     <t>Приближенное значение y при h=0,05</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>k1</t>
+  </si>
+  <si>
+    <t>k2</t>
+  </si>
+  <si>
+    <t>k3</t>
+  </si>
+  <si>
+    <t>k4</t>
+  </si>
+  <si>
+    <t>h=</t>
+  </si>
 </sst>
 </file>
 
@@ -37,13 +55,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,12 +91,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2503,6 +2532,423 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Метод</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> Рунге - Кутты</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'шаг 0,1'!$R$2:$R$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'шаг 0,1'!$S$2:$S$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.6750000000000013E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7461802812500007E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.1636844002355477E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.14064057783498135</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.21306186884675993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.29762386875263014</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.39317123734245796</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.49865857946885633</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.61313998240015133</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B4A4-4827-908C-C0692D3DD095}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="631501056"/>
+        <c:axId val="631496480"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="631501056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="631496480"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="631496480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="631501056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2663,6 +3109,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -4335,6 +4821,522 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4783,15 +5785,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4805,6 +5807,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5076,7 +6108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -5087,7 +6119,7 @@
     <col min="16" max="16" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>0</v>
       </c>
@@ -5104,8 +6136,23 @@
         <v>2</v>
       </c>
       <c r="P1" s="4"/>
+      <c r="R1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V1" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5150,8 +6197,30 @@
       <c r="O2" s="3">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>0.1*(2*R2-S2)</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="6">
+        <f>0.1*(2*(R2+0.05)-(S2+T2/2))</f>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="V2" s="6">
+        <f>0.1*(2*(R2+0.05)-(S2+U2/2))</f>
+        <v>9.5000000000000015E-3</v>
+      </c>
+      <c r="W2" s="6">
+        <f>0.1*(2*(R2+0.1)-(S2+V2))</f>
+        <v>1.9050000000000001E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5200,17 +6269,41 @@
       <c r="O3" s="3">
         <v>0</v>
       </c>
+      <c r="R3">
+        <f>R2+0.1</f>
+        <v>0.1</v>
+      </c>
+      <c r="S3">
+        <f>S2+(T2+2*(U2+V2)+W2)/6</f>
+        <v>9.6750000000000013E-3</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="3">0.1*(2*R3-S3)</f>
+        <v>1.9032500000000004E-2</v>
+      </c>
+      <c r="U3" s="6">
+        <f t="shared" ref="U3:U11" si="4">0.1*(2*(R3+0.05)-(S3+T3/2))</f>
+        <v>2.8080875000000005E-2</v>
+      </c>
+      <c r="V3" s="6">
+        <f t="shared" ref="V3:V11" si="5">0.1*(2*(R3+0.05)-(S3+U3/2))</f>
+        <v>2.7628456250000006E-2</v>
+      </c>
+      <c r="W3" s="6">
+        <f t="shared" ref="W3:W11" si="6">0.1*(2*(R3+0.1)-(S3+V3))</f>
+        <v>3.6269654375000009E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" ref="B4:B11" si="3">B3+0.1</f>
+        <f t="shared" ref="B4:B11" si="7">B3+0.1</f>
         <v>0.2</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C11" si="4">C3+0.1*(2*B3-C3)</f>
+        <f t="shared" ref="C4:C11" si="8">C3+0.1*(2*B3-C3)</f>
         <v>2.0000000000000004E-2</v>
       </c>
       <c r="D4" s="1">
@@ -5225,11 +6318,11 @@
         <v>3</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" ref="H4:H11" si="5">H3+0.1/2</f>
+        <f t="shared" ref="H4:H11" si="9">H3+0.1/2</f>
         <v>0.1</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" ref="I4:I11" si="6">I3+0.1/2*(2*H3-I3)</f>
+        <f t="shared" ref="I4:I11" si="10">I3+0.1/2*(2*H3-I3)</f>
         <v>5.000000000000001E-3</v>
       </c>
       <c r="J4" s="1">
@@ -5237,7 +6330,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" ref="K4:K10" si="7">0.1/2*(2*H4-I4)</f>
+        <f t="shared" ref="K4:K10" si="11">0.1/2*(2*H4-I4)</f>
         <v>9.7500000000000017E-3</v>
       </c>
       <c r="M4" s="3">
@@ -5250,17 +6343,41 @@
       <c r="O4" s="3">
         <v>5.000000000000001E-3</v>
       </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R11" si="12">R3+0.1</f>
+        <v>0.2</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S11" si="13">S3+(T3+2*(U3+V3)+W3)/6</f>
+        <v>3.7461802812500007E-2</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>3.6253819718750004E-2</v>
+      </c>
+      <c r="U4" s="6">
+        <f t="shared" si="4"/>
+        <v>4.4441128732812502E-2</v>
+      </c>
+      <c r="V4" s="6">
+        <f t="shared" si="5"/>
+        <v>4.4031763282109379E-2</v>
+      </c>
+      <c r="W4" s="6">
+        <f t="shared" si="6"/>
+        <v>5.1850643390539068E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.800000000000001E-2</v>
       </c>
       <c r="D5" s="1">
@@ -5275,11 +6392,11 @@
         <v>4</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.4750000000000003E-2</v>
       </c>
       <c r="J5" s="1">
@@ -5287,7 +6404,7 @@
         <v>0.28525000000000006</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.4262500000000004E-2</v>
       </c>
       <c r="M5" s="3">
@@ -5300,17 +6417,41 @@
       <c r="O5" s="3">
         <v>1.4750000000000003E-2</v>
       </c>
+      <c r="R5">
+        <f t="shared" si="12"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="13"/>
+        <v>8.1636844002355477E-2</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>5.1836315599764461E-2</v>
+      </c>
+      <c r="U5" s="6">
+        <f t="shared" si="4"/>
+        <v>5.9244499819776246E-2</v>
+      </c>
+      <c r="V5" s="6">
+        <f t="shared" si="5"/>
+        <v>5.8874090608775645E-2</v>
+      </c>
+      <c r="W5" s="6">
+        <f t="shared" si="6"/>
+        <v>6.5948906538886895E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.11220000000000002</v>
       </c>
       <c r="D6" s="1">
@@ -5325,11 +6466,11 @@
         <v>5</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.9012500000000007E-2</v>
       </c>
       <c r="J6" s="1">
@@ -5337,7 +6478,7 @@
         <v>0.37098750000000003</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.8549375000000003E-2</v>
       </c>
       <c r="M6" s="3">
@@ -5350,17 +6491,41 @@
       <c r="O6" s="3">
         <v>2.9012500000000007E-2</v>
       </c>
+      <c r="R6">
+        <f t="shared" si="12"/>
+        <v>0.4</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="13"/>
+        <v>0.14064057783498135</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>6.5935942216501883E-2</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" si="4"/>
+        <v>7.2639145105676775E-2</v>
+      </c>
+      <c r="V6" s="6">
+        <f t="shared" si="5"/>
+        <v>7.2303984961218024E-2</v>
+      </c>
+      <c r="W6" s="6">
+        <f t="shared" si="6"/>
+        <v>7.8705543720380064E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.18098000000000003</v>
       </c>
       <c r="D7" s="1">
@@ -5375,11 +6540,11 @@
         <v>6</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4.756187500000001E-2</v>
       </c>
       <c r="J7" s="1">
@@ -5387,7 +6552,7 @@
         <v>0.45243812499999997</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.2621906250000001E-2</v>
       </c>
       <c r="M7" s="3">
@@ -5400,17 +6565,41 @@
       <c r="O7" s="3">
         <v>4.756187500000001E-2</v>
       </c>
+      <c r="R7">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="13"/>
+        <v>0.21306186884675993</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>7.8693813115324016E-2</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="4"/>
+        <v>8.4759122459557815E-2</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="5"/>
+        <v>8.4455856992346132E-2</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="6"/>
+        <v>9.0248227416089399E-2</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.26288200000000006</v>
       </c>
       <c r="D8" s="1">
@@ -5425,11 +6614,11 @@
         <v>7</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.0183781250000007E-2</v>
       </c>
       <c r="J8" s="1">
@@ -5437,7 +6626,7 @@
         <v>0.52981621874999996</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6490810937499998E-2</v>
       </c>
       <c r="M8" s="3">
@@ -5450,17 +6639,41 @@
       <c r="O8" s="3">
         <v>7.0183781250000007E-2</v>
       </c>
+      <c r="R8">
+        <f t="shared" si="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="13"/>
+        <v>0.29762386875263014</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>9.0237613124736993E-2</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="4"/>
+        <v>9.5725732468500135E-2</v>
+      </c>
+      <c r="V8" s="6">
+        <f t="shared" si="5"/>
+        <v>9.5451326501311995E-2</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" si="6"/>
+        <v>0.10069248047460577</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.35659380000000007</v>
       </c>
       <c r="D9" s="1">
@@ -5475,11 +6688,11 @@
         <v>8</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9.6674592187500005E-2</v>
       </c>
       <c r="J9" s="1">
@@ -5487,7 +6700,7 @@
         <v>0.60332540781249999</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3.0166270390625E-2</v>
       </c>
       <c r="M9" s="3">
@@ -5500,17 +6713,41 @@
       <c r="O9" s="3">
         <v>9.6674592187500005E-2</v>
       </c>
+      <c r="R9">
+        <f t="shared" si="12"/>
+        <v>0.7</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="13"/>
+        <v>0.39317123734245796</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>0.10068287626575421</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="4"/>
+        <v>0.10564873245246649</v>
+      </c>
+      <c r="V9" s="6">
+        <f t="shared" si="5"/>
+        <v>0.10540043964313089</v>
+      </c>
+      <c r="W9" s="6">
+        <f t="shared" si="6"/>
+        <v>0.11014283230144112</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.46093442000000007</v>
       </c>
       <c r="D10" s="1">
@@ -5525,11 +6762,11 @@
         <v>9</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.12684086257812499</v>
       </c>
       <c r="J10" s="1">
@@ -5537,7 +6774,7 @@
         <v>0.67315913742187494</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3.3657956871093749E-2</v>
       </c>
       <c r="M10" s="3">
@@ -5550,17 +6787,41 @@
       <c r="O10" s="3">
         <v>0.12684086257812499</v>
       </c>
+      <c r="R10">
+        <f t="shared" si="12"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="13"/>
+        <v>0.49865857946885633</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>0.11013414205311436</v>
+      </c>
+      <c r="U10" s="6">
+        <f t="shared" si="4"/>
+        <v>0.11462743495045864</v>
+      </c>
+      <c r="V10" s="6">
+        <f t="shared" si="5"/>
+        <v>0.11440277030559143</v>
+      </c>
+      <c r="W10" s="6">
+        <f t="shared" si="6"/>
+        <v>0.11869386502255522</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.57484097800000011</v>
       </c>
       <c r="D11" s="1"/>
@@ -5569,11 +6830,11 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.16049881944921873</v>
       </c>
       <c r="J11" s="1"/>
@@ -5587,6 +6848,38 @@
       </c>
       <c r="O11" s="3">
         <v>0.16049881944921873</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="12"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="13"/>
+        <v>0.61313998240015133</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>0.11868600175998485</v>
+      </c>
+      <c r="U11" s="6">
+        <f t="shared" si="4"/>
+        <v>0.12275170167198562</v>
+      </c>
+      <c r="V11" s="6">
+        <f t="shared" si="5"/>
+        <v>0.12254841667638559</v>
+      </c>
+      <c r="W11" s="6">
+        <f t="shared" si="6"/>
+        <v>0.12643116009234628</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Q13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
